--- a/data/2b_pm_nh3_voc/static_tables/qa/2022/eGRID2022_pmemissions_subregion.xlsx
+++ b/data/2b_pm_nh3_voc/static_tables/qa/2022/eGRID2022_pmemissions_subregion.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet sheetId="1" r:id="rId1" name="Subregion_latest_NEI_yr_with_PM"/>
-    <sheet r:id="rId4" name="Subregion_latest_NEI_yr_with_P1" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="Subregion_latest_NEI_yr_with_PM">'Subregion_latest_NEI_yr_with_P1'!$A$1:$D$28</definedName>
+    <definedName name="Subregion_latest_NEI_yr_with_PM">'Subregion_latest_NEI_yr_with_PM'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -376,13 +375,13 @@
         </is>
       </c>
       <c r="B2" s="0">
-        <v>4923740</v>
+        <v>5016815</v>
       </c>
       <c r="C2" s="0">
-        <v>537.3</v>
+        <v>557.45</v>
       </c>
       <c r="D2" s="0">
-        <v>0.2182</v>
+        <v>0.2222</v>
       </c>
     </row>
     <row outlineLevel="0" r="3">
@@ -392,13 +391,13 @@
         </is>
       </c>
       <c r="B3" s="0">
-        <v>1672078</v>
+        <v>1677313</v>
       </c>
       <c r="C3" s="0">
-        <v>613.97</v>
+        <v>626.52</v>
       </c>
       <c r="D3" s="0">
-        <v>0.7344</v>
+        <v>0.7471</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
@@ -408,13 +407,13 @@
         </is>
       </c>
       <c r="B4" s="0">
-        <v>167984970</v>
+        <v>170369549</v>
       </c>
       <c r="C4" s="0">
-        <v>4144.02</v>
+        <v>4320.49</v>
       </c>
       <c r="D4" s="0">
-        <v>0.0493</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -424,13 +423,13 @@
         </is>
       </c>
       <c r="B5" s="0">
-        <v>204553916</v>
+        <v>209353986</v>
       </c>
       <c r="C5" s="0">
-        <v>2877.54</v>
+        <v>3951.89</v>
       </c>
       <c r="D5" s="0">
-        <v>0.0281</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row outlineLevel="0" r="6">
@@ -440,13 +439,13 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>421638208</v>
+        <v>458259386</v>
       </c>
       <c r="C6" s="0">
-        <v>10117.22</v>
+        <v>10909.05</v>
       </c>
       <c r="D6" s="0">
-        <v>0.048</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row outlineLevel="0" r="7">
@@ -456,13 +455,13 @@
         </is>
       </c>
       <c r="B7" s="0">
-        <v>237351634</v>
+        <v>250233811</v>
       </c>
       <c r="C7" s="0">
-        <v>7935.75</v>
+        <v>7917.91</v>
       </c>
       <c r="D7" s="0">
-        <v>0.0669</v>
+        <v>0.0633</v>
       </c>
     </row>
     <row outlineLevel="0" r="8">
@@ -472,13 +471,13 @@
         </is>
       </c>
       <c r="B8" s="0">
-        <v>2616354</v>
+        <v>2708213</v>
       </c>
       <c r="C8" s="0">
-        <v>1328.79</v>
+        <v>1034.15</v>
       </c>
       <c r="D8" s="0">
-        <v>1.0158</v>
+        <v>0.7637</v>
       </c>
     </row>
     <row outlineLevel="0" r="9">
@@ -488,13 +487,13 @@
         </is>
       </c>
       <c r="B9" s="0">
-        <v>6564236</v>
+        <v>6595979</v>
       </c>
       <c r="C9" s="0">
-        <v>1753.3</v>
+        <v>1828.96</v>
       </c>
       <c r="D9" s="0">
-        <v>0.5342</v>
+        <v>0.5546</v>
       </c>
     </row>
     <row outlineLevel="0" r="10">
@@ -504,13 +503,13 @@
         </is>
       </c>
       <c r="B10" s="0">
-        <v>24114781</v>
+        <v>22864489</v>
       </c>
       <c r="C10" s="0">
-        <v>700.54</v>
+        <v>673.18</v>
       </c>
       <c r="D10" s="0">
-        <v>0.0581</v>
+        <v>0.0589</v>
       </c>
     </row>
     <row outlineLevel="0" r="11">
@@ -520,13 +519,13 @@
         </is>
       </c>
       <c r="B11" s="0">
-        <v>242821306</v>
+        <v>251623837</v>
       </c>
       <c r="C11" s="0">
-        <v>6004.58</v>
+        <v>5631.62</v>
       </c>
       <c r="D11" s="0">
-        <v>0.0495</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row outlineLevel="0" r="12">
@@ -536,13 +535,13 @@
         </is>
       </c>
       <c r="B12" s="0">
-        <v>103068944</v>
+        <v>105455877</v>
       </c>
       <c r="C12" s="0">
-        <v>2329.63</v>
+        <v>2582.47</v>
       </c>
       <c r="D12" s="0">
-        <v>0.0452</v>
+        <v>0.049</v>
       </c>
     </row>
     <row outlineLevel="0" r="13">
@@ -552,13 +551,13 @@
         </is>
       </c>
       <c r="B13" s="0">
-        <v>282815849</v>
+        <v>290045161</v>
       </c>
       <c r="C13" s="0">
-        <v>5086.1</v>
+        <v>5476.41</v>
       </c>
       <c r="D13" s="0">
-        <v>0.036</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row outlineLevel="0" r="14">
@@ -568,13 +567,13 @@
         </is>
       </c>
       <c r="B14" s="0">
-        <v>32499681</v>
+        <v>32721381</v>
       </c>
       <c r="C14" s="0">
-        <v>948.38</v>
+        <v>1515.35</v>
       </c>
       <c r="D14" s="0">
-        <v>0.0584</v>
+        <v>0.0926</v>
       </c>
     </row>
     <row outlineLevel="0" r="15">
@@ -584,13 +583,13 @@
         </is>
       </c>
       <c r="B15" s="0">
-        <v>11938038</v>
+        <v>10828139</v>
       </c>
       <c r="C15" s="0">
-        <v>1305.46</v>
+        <v>1143.42</v>
       </c>
       <c r="D15" s="0">
-        <v>0.2187</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row outlineLevel="0" r="16">
@@ -600,13 +599,13 @@
         </is>
       </c>
       <c r="B16" s="0">
-        <v>85506174</v>
+        <v>87177697</v>
       </c>
       <c r="C16" s="0">
-        <v>691.82</v>
+        <v>752.51</v>
       </c>
       <c r="D16" s="0">
-        <v>0.0162</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row outlineLevel="0" r="17">
@@ -616,13 +615,13 @@
         </is>
       </c>
       <c r="B17" s="0">
-        <v>18578947</v>
+        <v>17762020</v>
       </c>
       <c r="C17" s="0">
-        <v>974.65</v>
+        <v>1177.37</v>
       </c>
       <c r="D17" s="0">
-        <v>0.1049</v>
+        <v>0.1326</v>
       </c>
     </row>
     <row outlineLevel="0" r="18">
@@ -632,13 +631,13 @@
         </is>
       </c>
       <c r="B18" s="0">
-        <v>290415250</v>
+        <v>289058252</v>
       </c>
       <c r="C18" s="0">
-        <v>-3118.15</v>
+        <v>4823.17</v>
       </c>
       <c r="D18" s="0">
-        <v>-0.0215</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row outlineLevel="0" r="19">
@@ -648,13 +647,13 @@
         </is>
       </c>
       <c r="B19" s="0">
-        <v>94434454</v>
+        <v>93807524</v>
       </c>
       <c r="C19" s="0">
-        <v>2160.7</v>
+        <v>3202.02</v>
       </c>
       <c r="D19" s="0">
-        <v>0.0458</v>
+        <v>0.0683</v>
       </c>
     </row>
     <row outlineLevel="0" r="20">
@@ -664,13 +663,13 @@
         </is>
       </c>
       <c r="B20" s="0">
-        <v>521426350</v>
+        <v>535522392</v>
       </c>
       <c r="C20" s="0">
-        <v>18445.96</v>
+        <v>17455.55</v>
       </c>
       <c r="D20" s="0">
-        <v>0.0708</v>
+        <v>0.0652</v>
       </c>
     </row>
     <row outlineLevel="0" r="21">
@@ -680,13 +679,13 @@
         </is>
       </c>
       <c r="B21" s="0">
-        <v>66044054</v>
+        <v>67125368</v>
       </c>
       <c r="C21" s="0">
-        <v>1348.96</v>
+        <v>1629.53</v>
       </c>
       <c r="D21" s="0">
-        <v>0.0409</v>
+        <v>0.0486</v>
       </c>
     </row>
     <row outlineLevel="0" r="22">
@@ -696,13 +695,13 @@
         </is>
       </c>
       <c r="B22" s="0">
-        <v>73370171</v>
+        <v>78559613</v>
       </c>
       <c r="C22" s="0">
-        <v>1393.19</v>
+        <v>1339.08</v>
       </c>
       <c r="D22" s="0">
-        <v>0.038</v>
+        <v>0.0341</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
@@ -712,13 +711,13 @@
         </is>
       </c>
       <c r="B23" s="0">
-        <v>148803953</v>
+        <v>155729281</v>
       </c>
       <c r="C23" s="0">
-        <v>3442.55</v>
+        <v>3241.85</v>
       </c>
       <c r="D23" s="0">
-        <v>0.0463</v>
+        <v>0.0416</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
@@ -728,13 +727,13 @@
         </is>
       </c>
       <c r="B24" s="0">
-        <v>171263642</v>
+        <v>183054493</v>
       </c>
       <c r="C24" s="0">
-        <v>4356.95</v>
+        <v>5290.83</v>
       </c>
       <c r="D24" s="0">
-        <v>0.0509</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
@@ -744,13 +743,13 @@
         </is>
       </c>
       <c r="B25" s="0">
-        <v>114130604</v>
+        <v>118737335</v>
       </c>
       <c r="C25" s="0">
-        <v>5657.58</v>
+        <v>4098.28</v>
       </c>
       <c r="D25" s="0">
-        <v>0.0991</v>
+        <v>0.069</v>
       </c>
     </row>
     <row outlineLevel="0" r="26">
@@ -760,13 +759,13 @@
         </is>
       </c>
       <c r="B26" s="0">
-        <v>253393159</v>
+        <v>257187544</v>
       </c>
       <c r="C26" s="0">
-        <v>3984.43</v>
+        <v>5499.7</v>
       </c>
       <c r="D26" s="0">
-        <v>0.0314</v>
+        <v>0.0428</v>
       </c>
     </row>
     <row outlineLevel="0" r="27">
@@ -776,13 +775,13 @@
         </is>
       </c>
       <c r="B27" s="0">
-        <v>214888097</v>
+        <v>214916301</v>
       </c>
       <c r="C27" s="0">
-        <v>21879.64</v>
+        <v>6203.57</v>
       </c>
       <c r="D27" s="0">
-        <v>0.2036</v>
+        <v>0.0577</v>
       </c>
     </row>
     <row outlineLevel="0" r="28">
@@ -792,477 +791,13 @@
         </is>
       </c>
       <c r="B28" s="0">
-        <v>323326029</v>
+        <v>323748776</v>
       </c>
       <c r="C28" s="0">
-        <v>8023.66</v>
+        <v>7652.53</v>
       </c>
       <c r="D28" s="0">
-        <v>0.0496</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row outlineLevel="0" r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>SUBRGN</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>Gen</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>PM25tons</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-    </row>
-    <row outlineLevel="0" r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>AKGD</t>
-        </is>
-      </c>
-      <c r="B2" s="0">
-        <v>5016815</v>
-      </c>
-      <c r="C2" s="0">
-        <v>557.45</v>
-      </c>
-      <c r="D2" s="0">
-        <v>0.2222</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>AKMS</t>
-        </is>
-      </c>
-      <c r="B3" s="0">
-        <v>1677313</v>
-      </c>
-      <c r="C3" s="0">
-        <v>626.52</v>
-      </c>
-      <c r="D3" s="0">
-        <v>0.7471</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>AZNM</t>
-        </is>
-      </c>
-      <c r="B4" s="0">
-        <v>170369549</v>
-      </c>
-      <c r="C4" s="0">
-        <v>4320.49</v>
-      </c>
-      <c r="D4" s="0">
-        <v>0.0507</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>CAMX</t>
-        </is>
-      </c>
-      <c r="B5" s="0">
-        <v>209353986</v>
-      </c>
-      <c r="C5" s="0">
-        <v>3955.25</v>
-      </c>
-      <c r="D5" s="0">
-        <v>0.0378</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>ERCT</t>
-        </is>
-      </c>
-      <c r="B6" s="0">
-        <v>458259386</v>
-      </c>
-      <c r="C6" s="0">
-        <v>10909.22</v>
-      </c>
-      <c r="D6" s="0">
-        <v>0.0476</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>FRCC</t>
-        </is>
-      </c>
-      <c r="B7" s="0">
-        <v>250233811</v>
-      </c>
-      <c r="C7" s="0">
-        <v>7951.17</v>
-      </c>
-      <c r="D7" s="0">
-        <v>0.0635</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>HIMS</t>
-        </is>
-      </c>
-      <c r="B8" s="0">
-        <v>2708213</v>
-      </c>
-      <c r="C8" s="0">
-        <v>1034.15</v>
-      </c>
-      <c r="D8" s="0">
-        <v>0.7637</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>HIOA</t>
-        </is>
-      </c>
-      <c r="B9" s="0">
-        <v>6595979</v>
-      </c>
-      <c r="C9" s="0">
-        <v>1834.57</v>
-      </c>
-      <c r="D9" s="0">
-        <v>0.5563</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>MROE</t>
-        </is>
-      </c>
-      <c r="B10" s="0">
-        <v>22864489</v>
-      </c>
-      <c r="C10" s="0">
-        <v>673.18</v>
-      </c>
-      <c r="D10" s="0">
-        <v>0.0589</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>MROW</t>
-        </is>
-      </c>
-      <c r="B11" s="0">
-        <v>251623837</v>
-      </c>
-      <c r="C11" s="0">
-        <v>5636.27</v>
-      </c>
-      <c r="D11" s="0">
-        <v>0.0448</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>NEWE</t>
-        </is>
-      </c>
-      <c r="B12" s="0">
-        <v>105455877</v>
-      </c>
-      <c r="C12" s="0">
-        <v>2702.57</v>
-      </c>
-      <c r="D12" s="0">
-        <v>0.0513</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>NWPP</t>
-        </is>
-      </c>
-      <c r="B13" s="0">
-        <v>290045161</v>
-      </c>
-      <c r="C13" s="0">
-        <v>5496.23</v>
-      </c>
-      <c r="D13" s="0">
-        <v>0.0379</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>NYCW</t>
-        </is>
-      </c>
-      <c r="B14" s="0">
-        <v>32721381</v>
-      </c>
-      <c r="C14" s="0">
-        <v>1545.21</v>
-      </c>
-      <c r="D14" s="0">
-        <v>0.0944</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>NYLI</t>
-        </is>
-      </c>
-      <c r="B15" s="0">
-        <v>10828139</v>
-      </c>
-      <c r="C15" s="0">
-        <v>1146.88</v>
-      </c>
-      <c r="D15" s="0">
-        <v>0.2118</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>NYUP</t>
-        </is>
-      </c>
-      <c r="B16" s="0">
-        <v>87177697</v>
-      </c>
-      <c r="C16" s="0">
-        <v>767.17</v>
-      </c>
-      <c r="D16" s="0">
-        <v>0.0176</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>PRMS</t>
-        </is>
-      </c>
-      <c r="B17" s="0">
-        <v>17762020</v>
-      </c>
-      <c r="C17" s="0">
-        <v>1177.37</v>
-      </c>
-      <c r="D17" s="0">
-        <v>0.1326</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t>RFCE</t>
-        </is>
-      </c>
-      <c r="B18" s="0">
-        <v>289058252</v>
-      </c>
-      <c r="C18" s="0">
-        <v>-2935.01</v>
-      </c>
-      <c r="D18" s="0">
-        <v>-0.0203</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>RFCM</t>
-        </is>
-      </c>
-      <c r="B19" s="0">
-        <v>93807524</v>
-      </c>
-      <c r="C19" s="0">
-        <v>3202.18</v>
-      </c>
-      <c r="D19" s="0">
-        <v>0.0683</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t>RFCW</t>
-        </is>
-      </c>
-      <c r="B20" s="0">
-        <v>535522392</v>
-      </c>
-      <c r="C20" s="0">
-        <v>17455.55</v>
-      </c>
-      <c r="D20" s="0">
-        <v>0.0652</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t>RMPA</t>
-        </is>
-      </c>
-      <c r="B21" s="0">
-        <v>67125368</v>
-      </c>
-      <c r="C21" s="0">
-        <v>1629.53</v>
-      </c>
-      <c r="D21" s="0">
-        <v>0.0486</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t>SPNO</t>
-        </is>
-      </c>
-      <c r="B22" s="0">
-        <v>78559613</v>
-      </c>
-      <c r="C22" s="0">
-        <v>1339.08</v>
-      </c>
-      <c r="D22" s="0">
-        <v>0.0341</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="23">
-      <c r="A23" s="0" t="inlineStr">
-        <is>
-          <t>SPSO</t>
-        </is>
-      </c>
-      <c r="B23" s="0">
-        <v>155729281</v>
-      </c>
-      <c r="C23" s="0">
-        <v>3244.95</v>
-      </c>
-      <c r="D23" s="0">
-        <v>0.0417</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t>SRMV</t>
-        </is>
-      </c>
-      <c r="B24" s="0">
-        <v>183054493</v>
-      </c>
-      <c r="C24" s="0">
-        <v>5297.49</v>
-      </c>
-      <c r="D24" s="0">
-        <v>0.0579</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="25">
-      <c r="A25" s="0" t="inlineStr">
-        <is>
-          <t>SRMW</t>
-        </is>
-      </c>
-      <c r="B25" s="0">
-        <v>118737335</v>
-      </c>
-      <c r="C25" s="0">
-        <v>4098.28</v>
-      </c>
-      <c r="D25" s="0">
-        <v>0.069</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t>SRSO</t>
-        </is>
-      </c>
-      <c r="B26" s="0">
-        <v>257187544</v>
-      </c>
-      <c r="C26" s="0">
-        <v>5499.7</v>
-      </c>
-      <c r="D26" s="0">
-        <v>0.0428</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="27">
-      <c r="A27" s="0" t="inlineStr">
-        <is>
-          <t>SRTV</t>
-        </is>
-      </c>
-      <c r="B27" s="0">
-        <v>214916301</v>
-      </c>
-      <c r="C27" s="0">
-        <v>6203.57</v>
-      </c>
-      <c r="D27" s="0">
-        <v>0.0577</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="28">
-      <c r="A28" s="0" t="inlineStr">
-        <is>
-          <t>SRVC</t>
-        </is>
-      </c>
-      <c r="B28" s="0">
-        <v>323748776</v>
-      </c>
-      <c r="C28" s="0">
-        <v>7686.87</v>
-      </c>
-      <c r="D28" s="0">
-        <v>0.0475</v>
+        <v>0.0473</v>
       </c>
     </row>
   </sheetData>
@@ -1542,22 +1077,29 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="6c854b04-c9c6-4391-adbe-2e73191270e7" xsi:nil="true"/>
+    <SharedWithUsers xmlns="c05e7bd6-26a7-41a1-805c-893279a3732f">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="059b9c67-646b-4b4e-9ab1-2b1c805d0390">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6c854b04-c9c6-4391-adbe-2e73191270e7" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3285950A-8E74-445F-BEA3-2FB53B5BF61F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8171C257-AFF4-4533-88BC-F8A2BED61D02}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DDD3B61-A896-4C39-999F-0A89E64DDA64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7B76074-5050-437A-A945-4E8AAEE34E8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A6A4DF7-AADF-4CCC-A361-28614356EFC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD467696-9916-4AAD-8990-39441443EE71}"/>
 </file>
--- a/data/2b_pm_nh3_voc/static_tables/qa/2022/eGRID2022_pmemissions_subregion.xlsx
+++ b/data/2b_pm_nh3_voc/static_tables/qa/2022/eGRID2022_pmemissions_subregion.xlsx
@@ -426,7 +426,7 @@
         <v>209353986</v>
       </c>
       <c r="C5" s="0">
-        <v>3951.89</v>
+        <v>3955.25</v>
       </c>
       <c r="D5" s="0">
         <v>0.0378</v>
@@ -442,7 +442,7 @@
         <v>458259386</v>
       </c>
       <c r="C6" s="0">
-        <v>10909.05</v>
+        <v>10909.22</v>
       </c>
       <c r="D6" s="0">
         <v>0.0476</v>
@@ -458,10 +458,10 @@
         <v>250233811</v>
       </c>
       <c r="C7" s="0">
-        <v>7917.91</v>
+        <v>8170.04</v>
       </c>
       <c r="D7" s="0">
-        <v>0.0633</v>
+        <v>0.0653</v>
       </c>
     </row>
     <row outlineLevel="0" r="8">
@@ -490,10 +490,10 @@
         <v>6595979</v>
       </c>
       <c r="C9" s="0">
-        <v>1828.96</v>
+        <v>1834.57</v>
       </c>
       <c r="D9" s="0">
-        <v>0.5546</v>
+        <v>0.5563</v>
       </c>
     </row>
     <row outlineLevel="0" r="10">
@@ -522,7 +522,7 @@
         <v>251623837</v>
       </c>
       <c r="C11" s="0">
-        <v>5631.62</v>
+        <v>5636.28</v>
       </c>
       <c r="D11" s="0">
         <v>0.0448</v>
@@ -538,10 +538,10 @@
         <v>105455877</v>
       </c>
       <c r="C12" s="0">
-        <v>2582.47</v>
+        <v>2698.91</v>
       </c>
       <c r="D12" s="0">
-        <v>0.049</v>
+        <v>0.0512</v>
       </c>
     </row>
     <row outlineLevel="0" r="13">
@@ -554,10 +554,10 @@
         <v>290045161</v>
       </c>
       <c r="C13" s="0">
-        <v>5476.41</v>
+        <v>5588.63</v>
       </c>
       <c r="D13" s="0">
-        <v>0.0378</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row outlineLevel="0" r="14">
@@ -570,10 +570,10 @@
         <v>32721381</v>
       </c>
       <c r="C14" s="0">
-        <v>1515.35</v>
+        <v>1537.07</v>
       </c>
       <c r="D14" s="0">
-        <v>0.0926</v>
+        <v>0.0939</v>
       </c>
     </row>
     <row outlineLevel="0" r="15">
@@ -586,10 +586,10 @@
         <v>10828139</v>
       </c>
       <c r="C15" s="0">
-        <v>1143.42</v>
+        <v>1146.88</v>
       </c>
       <c r="D15" s="0">
-        <v>0.2112</v>
+        <v>0.2118</v>
       </c>
     </row>
     <row outlineLevel="0" r="16">
@@ -602,10 +602,10 @@
         <v>87177697</v>
       </c>
       <c r="C16" s="0">
-        <v>752.51</v>
+        <v>762.41</v>
       </c>
       <c r="D16" s="0">
-        <v>0.0173</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row outlineLevel="0" r="17">
@@ -634,10 +634,10 @@
         <v>289058252</v>
       </c>
       <c r="C18" s="0">
-        <v>4823.17</v>
+        <v>4857.61</v>
       </c>
       <c r="D18" s="0">
-        <v>0.0334</v>
+        <v>0.0336</v>
       </c>
     </row>
     <row outlineLevel="0" r="19">
@@ -650,7 +650,7 @@
         <v>93807524</v>
       </c>
       <c r="C19" s="0">
-        <v>3202.02</v>
+        <v>3202.27</v>
       </c>
       <c r="D19" s="0">
         <v>0.0683</v>
@@ -714,10 +714,10 @@
         <v>155729281</v>
       </c>
       <c r="C23" s="0">
-        <v>3241.85</v>
+        <v>3244.95</v>
       </c>
       <c r="D23" s="0">
-        <v>0.0416</v>
+        <v>0.0417</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
@@ -730,10 +730,10 @@
         <v>183054493</v>
       </c>
       <c r="C24" s="0">
-        <v>5290.83</v>
+        <v>5297.49</v>
       </c>
       <c r="D24" s="0">
-        <v>0.0578</v>
+        <v>0.0579</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
@@ -794,10 +794,10 @@
         <v>323748776</v>
       </c>
       <c r="C28" s="0">
-        <v>7652.53</v>
+        <v>7688</v>
       </c>
       <c r="D28" s="0">
-        <v>0.0473</v>
+        <v>0.0475</v>
       </c>
     </row>
   </sheetData>
@@ -1077,29 +1077,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <SharedWithUsers xmlns="c05e7bd6-26a7-41a1-805c-893279a3732f">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
+    <TaxCatchAll xmlns="6c854b04-c9c6-4391-adbe-2e73191270e7" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="059b9c67-646b-4b4e-9ab1-2b1c805d0390">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6c854b04-c9c6-4391-adbe-2e73191270e7" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8171C257-AFF4-4533-88BC-F8A2BED61D02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D48300E-5D61-48A3-A220-E6E9F064C2B0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7B76074-5050-437A-A945-4E8AAEE34E8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AF073F2-51E8-4958-BFD6-0DB48579DE03}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD467696-9916-4AAD-8990-39441443EE71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF201369-56BF-4C58-AABF-96D5B3F4838D}"/>
 </file>
--- a/data/2b_pm_nh3_voc/static_tables/qa/2022/eGRID2022_pmemissions_subregion.xlsx
+++ b/data/2b_pm_nh3_voc/static_tables/qa/2022/eGRID2022_pmemissions_subregion.xlsx
@@ -378,7 +378,7 @@
         <v>5016815</v>
       </c>
       <c r="C2" s="0">
-        <v>557.45</v>
+        <v>557.44</v>
       </c>
       <c r="D2" s="0">
         <v>0.2222</v>
@@ -394,10 +394,10 @@
         <v>1677313</v>
       </c>
       <c r="C3" s="0">
-        <v>626.52</v>
+        <v>626.5</v>
       </c>
       <c r="D3" s="0">
-        <v>0.7471</v>
+        <v>0.747</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
@@ -410,7 +410,7 @@
         <v>170369549</v>
       </c>
       <c r="C4" s="0">
-        <v>4320.49</v>
+        <v>4320.39</v>
       </c>
       <c r="D4" s="0">
         <v>0.0507</v>
@@ -426,7 +426,7 @@
         <v>209353986</v>
       </c>
       <c r="C5" s="0">
-        <v>3955.25</v>
+        <v>3954.65</v>
       </c>
       <c r="D5" s="0">
         <v>0.0378</v>
@@ -442,7 +442,7 @@
         <v>458259386</v>
       </c>
       <c r="C6" s="0">
-        <v>10909.22</v>
+        <v>10908.51</v>
       </c>
       <c r="D6" s="0">
         <v>0.0476</v>
@@ -458,7 +458,7 @@
         <v>250233811</v>
       </c>
       <c r="C7" s="0">
-        <v>8170.04</v>
+        <v>8169.95</v>
       </c>
       <c r="D7" s="0">
         <v>0.0653</v>
@@ -522,7 +522,7 @@
         <v>251623837</v>
       </c>
       <c r="C11" s="0">
-        <v>5636.28</v>
+        <v>5636.19</v>
       </c>
       <c r="D11" s="0">
         <v>0.0448</v>
@@ -538,7 +538,7 @@
         <v>105455877</v>
       </c>
       <c r="C12" s="0">
-        <v>2698.91</v>
+        <v>2698.83</v>
       </c>
       <c r="D12" s="0">
         <v>0.0512</v>
@@ -554,7 +554,7 @@
         <v>290045161</v>
       </c>
       <c r="C13" s="0">
-        <v>5588.63</v>
+        <v>5588.44</v>
       </c>
       <c r="D13" s="0">
         <v>0.0385</v>
@@ -570,7 +570,7 @@
         <v>32721381</v>
       </c>
       <c r="C14" s="0">
-        <v>1537.07</v>
+        <v>1537.06</v>
       </c>
       <c r="D14" s="0">
         <v>0.0939</v>
@@ -586,7 +586,7 @@
         <v>10828139</v>
       </c>
       <c r="C15" s="0">
-        <v>1146.88</v>
+        <v>1146.86</v>
       </c>
       <c r="D15" s="0">
         <v>0.2118</v>
@@ -602,7 +602,7 @@
         <v>87177697</v>
       </c>
       <c r="C16" s="0">
-        <v>762.41</v>
+        <v>762.4</v>
       </c>
       <c r="D16" s="0">
         <v>0.0175</v>
@@ -634,10 +634,10 @@
         <v>289058252</v>
       </c>
       <c r="C18" s="0">
-        <v>4857.61</v>
+        <v>4844.86</v>
       </c>
       <c r="D18" s="0">
-        <v>0.0336</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row outlineLevel="0" r="19">
@@ -650,7 +650,7 @@
         <v>93807524</v>
       </c>
       <c r="C19" s="0">
-        <v>3202.27</v>
+        <v>3202.23</v>
       </c>
       <c r="D19" s="0">
         <v>0.0683</v>
@@ -666,7 +666,7 @@
         <v>535522392</v>
       </c>
       <c r="C20" s="0">
-        <v>17455.55</v>
+        <v>17455.25</v>
       </c>
       <c r="D20" s="0">
         <v>0.0652</v>
@@ -682,7 +682,7 @@
         <v>67125368</v>
       </c>
       <c r="C21" s="0">
-        <v>1629.53</v>
+        <v>1629.52</v>
       </c>
       <c r="D21" s="0">
         <v>0.0486</v>
@@ -698,7 +698,7 @@
         <v>78559613</v>
       </c>
       <c r="C22" s="0">
-        <v>1339.08</v>
+        <v>1339.05</v>
       </c>
       <c r="D22" s="0">
         <v>0.0341</v>
@@ -714,7 +714,7 @@
         <v>155729281</v>
       </c>
       <c r="C23" s="0">
-        <v>3244.95</v>
+        <v>3244.78</v>
       </c>
       <c r="D23" s="0">
         <v>0.0417</v>
@@ -730,7 +730,7 @@
         <v>183054493</v>
       </c>
       <c r="C24" s="0">
-        <v>5297.49</v>
+        <v>5296.91</v>
       </c>
       <c r="D24" s="0">
         <v>0.0579</v>
@@ -746,7 +746,7 @@
         <v>118737335</v>
       </c>
       <c r="C25" s="0">
-        <v>4098.28</v>
+        <v>4098.25</v>
       </c>
       <c r="D25" s="0">
         <v>0.069</v>
@@ -762,7 +762,7 @@
         <v>257187544</v>
       </c>
       <c r="C26" s="0">
-        <v>5499.7</v>
+        <v>5499.58</v>
       </c>
       <c r="D26" s="0">
         <v>0.0428</v>
@@ -778,7 +778,7 @@
         <v>214916301</v>
       </c>
       <c r="C27" s="0">
-        <v>6203.57</v>
+        <v>6203.51</v>
       </c>
       <c r="D27" s="0">
         <v>0.0577</v>
@@ -794,7 +794,7 @@
         <v>323748776</v>
       </c>
       <c r="C28" s="0">
-        <v>7688</v>
+        <v>7687.96</v>
       </c>
       <c r="D28" s="0">
         <v>0.0475</v>
@@ -1086,13 +1086,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D48300E-5D61-48A3-A220-E6E9F064C2B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{177136DE-EC9D-4A6A-98D4-916097AE5356}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AF073F2-51E8-4958-BFD6-0DB48579DE03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F1A90E2-24B2-4136-9D52-751C7F908691}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF201369-56BF-4C58-AABF-96D5B3F4838D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FEF3D45-672F-4512-AA08-F94F1DFC40F2}"/>
 </file>